--- a/AAII_Financials/Quarterly/BX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>BX</t>
   </si>
@@ -656,299 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4887000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3429600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4233100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2933600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3801100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3245000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2811500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3648200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2668100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3534800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1287200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2366900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2738300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1291600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1704100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1058100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>629200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5126300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5762700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6224300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5291400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5298900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3628900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3032900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2516100</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD8" s="3">
         <v>2091500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1735100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1486800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2024900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>505000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1926600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2632600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1769100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1959200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1735400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1535700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1914700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1569400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1431700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1051,71 +1058,74 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="3">
         <v>407900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>368000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>311900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>407700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>313800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>267400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4887000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3429600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4233100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2933600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3801100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3245000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2811500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3648200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2668100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3534800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1287200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2366900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2738300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1291600</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1173,26 +1183,29 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="3">
         <v>1551300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1367400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1223800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1507000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1255600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1164300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1508,74 +1528,74 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>17800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>56800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>49100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>-21500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-32000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>37300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>27200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>7700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>13000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-174600</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>5</v>
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>5</v>
@@ -1583,71 +1603,74 @@
       <c r="AJ14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL14" s="3">
         <v>-403900</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E15" s="3">
         <v>26100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>62100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>22200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>58600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>30600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>56300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2230600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2125200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1996800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1624400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1796800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1776300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1384600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1784800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1524100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1682200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>832800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1264300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1367200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1084900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1049000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>961400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>744100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2196300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2466400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2691700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2272700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2048500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1639300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1340500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1172600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>-637500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1127100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>772600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>862200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1041200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>495100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1017600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1016400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>982900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>641000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>904500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>881200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>921800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>824500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>773800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2656400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1304300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2236300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1309200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2004400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1468600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1426900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1863400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1144000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1852600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>454300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1102600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1371000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>206700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>655100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>96700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-114900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2930000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3296300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3532600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3018700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3250400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1989600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1692400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1343500</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>964400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>962500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>624600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>983700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>909000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1616200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>786200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1318200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>830900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>654500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>992900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>744900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>657900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,252 +2085,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-51000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-28700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>225100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>73600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-114300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>96300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-19600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-44800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>140000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-63800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>24600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>19400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-52900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-104300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>50900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>81800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>132300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>127100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>120300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>90900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>108800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>158300</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>42900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>48500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>61100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>130300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-59300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>66800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>73500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>110600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>82000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>63400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>110100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>66200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>73500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2694100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1381400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2304100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1362000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1805900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1417300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1599800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1791800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1189000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1923500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>348600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1197000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1402800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>200300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>617000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>112800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2999600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3396800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3683600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3164400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3389500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2098300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1818900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1519500</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>1025100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1028700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>703400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1131800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-33800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>990300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1704200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>911300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1414000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>905300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>775600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1070000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>834000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>741000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2808500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1455100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2356800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1446600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1915600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1452600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1561300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1809900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1208600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1879700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>155100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1117300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1427000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>258400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>602200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>97900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-219200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2980900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3378100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3664900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3145700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3370700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2080500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1801100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1501800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2765900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1007300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1010900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>685700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1114000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-49400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>975800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1689700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>896800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1400100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>894300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>764600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1059100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>818400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>719300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>452400</v>
+      </c>
+      <c r="E24" s="3">
         <v>197200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>382000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>209700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>289500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>243800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>232500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>245300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>260200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>283700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>196600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>223300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>47700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-141100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>94200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>36500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>483300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>437700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>458900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>288300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>266300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>101000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>147400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-158700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>28900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-156800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>38700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>41200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>29400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>26800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>138700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>54500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>256300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>59500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>29600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>57400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>48100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2356100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1257900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1974800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1236900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1626100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1208800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1328800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1564600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>948400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1596000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>109100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>920700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1203700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>210700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>743300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-255700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2497600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2940400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3206000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2857500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3371100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1814200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1700200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1354300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2607200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>978400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1167700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>647000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1072900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-78700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>949000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1551000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>842300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1143800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>834800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>735000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1001600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>770300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>691600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1229200</v>
+      </c>
+      <c r="E27" s="3">
         <v>649700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1015200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>624900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>764200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>614900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>703900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>780800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>444400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>847400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>151800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>552000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>601300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>85800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>557900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-29400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1216900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1398500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1401900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1309200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1747900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>748900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>794700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>568300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1066500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>483100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>779400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>305800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>481300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>442700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>742000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>367900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>644400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>377900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>337400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>451900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>368000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>312900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-340300</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E32" s="3">
         <v>51000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>28700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-225100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-73600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>114300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-96300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>19600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>44800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-140000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>63800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-24600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>52900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>104300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-50900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-81800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-132300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-127100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-120300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-90900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-108800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-158300</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-42900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-48500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-61100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-130300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>59300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-66800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-73500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-110600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-82000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-63400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-110100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-66200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-73500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-61400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1229200</v>
+      </c>
+      <c r="E33" s="3">
         <v>649700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1015200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>624900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>764200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>614900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>703900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>780800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>444400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>847400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>151800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>552000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>601300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>85800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>557900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-29400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1216900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1398500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1401900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1309200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1747900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>748900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>794700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>568300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1066500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>483100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>779400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>305800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>481300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>442700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>742000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>367900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>304100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>377900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>337400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>451900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>368000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>312900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1229200</v>
+      </c>
+      <c r="E35" s="3">
         <v>649700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1015200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>624900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>764200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>614900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>703900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>780800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>444400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>847400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>151800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>552000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>601300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>85800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>557900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-29400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1216900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1398500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1401900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1309200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1747900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>748900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>794700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>568300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1066500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>483100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>779400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>305800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>481300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>442700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>742000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>367900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>304100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>377900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>337400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>451900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>368000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>312900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2507100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2448500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2631200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2430700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2235500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2387000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1972100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2353300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2381400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2504500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2955900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2971600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3280200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2831000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4493700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3574400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4312700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3979200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2199700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5125200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2577100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2971700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2064500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2714100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2319700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2386300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2523700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2844500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1809100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1788400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2545200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2346500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1998900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2450100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3922000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2981400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3271600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3720600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2842400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2890800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E42" s="3">
         <v>156600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>134600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>123800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>125700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>175100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>180300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>141900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>189000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>163700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>170900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>222000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>186100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>184800</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6910100</v>
+      </c>
+      <c r="E43" s="3">
         <v>6968000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6649200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6389100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5874700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5655300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5647200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5463900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5115600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4894500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4659900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5092100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4958500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5024700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4609600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4865000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4666100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4521800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5293500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4214400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3742400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3990900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4087700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3294900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2930100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3402800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3569900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3219900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3013800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3032200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2630400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2893300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2933700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2591300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2903200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2933100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2820900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2943300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2215100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1817300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,113 +4803,116 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>239000</v>
+      </c>
+      <c r="E45" s="3">
         <v>292500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>315300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>192500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>169000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>181200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>192800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>247900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>343500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>314900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>207900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>190400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>201700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>168700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>165100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>123600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>183500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>76100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>92400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>203100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>193900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>110800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>105200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>177900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>144800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>177000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>159300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>149100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>159400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>139900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>110700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>96200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>90700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>90100</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10070600</v>
+      </c>
+      <c r="E46" s="3">
         <v>10127600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9953800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9537700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8718800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9411500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8196500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8387600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8249000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8045200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8310700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8614300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8841900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8399500</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,235 +5053,241 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34587700</v>
+      </c>
+      <c r="E47" s="3">
         <v>32747600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>32212100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>31528400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>31135500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>30259400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29800600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28322700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26426300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>25922300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>26146600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>27339900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>27030300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>26966400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>27553300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>26256100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>27323800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>30068500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>28665000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>25104200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>22163300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>17943300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>15617100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>14423500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>18973400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>16430700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>22281700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>22204500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>22242000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>21181000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>20377000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22094900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>22008200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>19763600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>24434000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>22385200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>20549400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>18182900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>17813500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>16047300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1280200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1317100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1278600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1297700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1318500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1321100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1344900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1495600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1517500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1340100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1384100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1401100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1383300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1352400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1308700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1274900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1203300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1155100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1033600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>985000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>965600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>977100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>758800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>744900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>733200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>702300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>625500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>641800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>649100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>655500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>120400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>116600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>122300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>124000</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5195,130 +5303,136 @@
       <c r="AP48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2003500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2012500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2021600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2030700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2037500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2046500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2055400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2064500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2073400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2082400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2091400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2100400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2109400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2120500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2107500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2122300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2137200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2155900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2174600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2193300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2212000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2230700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2249400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2214100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2231900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2249600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2267400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2285100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2302900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2320600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2338400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2144600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2159000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2173500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2188000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1948200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1959200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1970200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1981100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1996700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E52" s="3">
         <v>55200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>186600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>59600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>57500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>59200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>68500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>27300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>59400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>23200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>40900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2062700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1767900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1646400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1327500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1581600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1116600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1322100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1402300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1242600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1305700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1319300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1392400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1089300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>938200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>743100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>728900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>739500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>711600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>722600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>718400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>726000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1260900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1292700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1263100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1286500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1287900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49892200</v>
+      </c>
+      <c r="E54" s="3">
         <v>48327000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47709000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>46554300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45373100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45255600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43469900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42575400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40585000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39706300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40287500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41663800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41582800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41086400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42524200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40259300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>41631300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43344100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41196400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>39038100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33297200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29710000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26269300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25041600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28844400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>26946500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>32585500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>32385800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30972200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29875000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28924700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30460400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>30075300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>27933400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>34415900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>31762000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>30127900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>28337200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>26403300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>24413500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,252 +6145,259 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1830700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1840200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1316100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1717500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1273700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1339700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1462300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1247400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1146900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1274100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1406300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1198600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1285600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1509600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1158100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1141900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>991600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1053100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>937200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>871700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1205200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>838900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>717100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>804000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>919200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1000700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>806200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1069500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>929700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>735700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>876000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>829500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>950800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1252200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2043500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1395000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1739400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2943100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2403600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2283800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2877400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3068500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2123200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1396000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2119900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1597500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1391600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1333700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1271400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>868600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>654600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>427300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>186500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>203700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>93800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>339900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>179600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>104600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>85800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>72200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>93000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>91200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>127800</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>80600</v>
       </c>
       <c r="AA58" s="3">
         <v>80600</v>
       </c>
       <c r="AB58" s="3">
+        <v>80600</v>
+      </c>
+      <c r="AC58" s="3">
         <v>105100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>154100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>163100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>207700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>218900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>222200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>199500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>182500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>142500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>273200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>180200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>204400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>273100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>290700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>238300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6277,16 +6414,16 @@
         <v>2000</v>
       </c>
       <c r="H59" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="I59" s="3">
         <v>1900</v>
       </c>
       <c r="J59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K59" s="3">
         <v>4000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3900</v>
       </c>
       <c r="L59" s="3">
         <v>3900</v>
@@ -6294,140 +6431,143 @@
       <c r="M59" s="3">
         <v>3900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="N59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9241700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9779000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9760800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11007900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10719200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9688800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7857300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6380700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5189100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5035200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4457600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3818100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5365900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5166500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4965100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4634500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3977900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4396200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3955200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3539100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3560700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4143500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3738400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2221200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2327800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2292700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11554200</v>
+      </c>
+      <c r="E60" s="3">
         <v>11307000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9852700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9501500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9461600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9103600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8943500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8983400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8125300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7524800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7312600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7609100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7161900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7188000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,175 +6643,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12418700</v>
+      </c>
+      <c r="E61" s="3">
         <v>12356200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12434500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12690100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12029300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12923900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11970800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11504600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11419300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11567200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12293900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13055800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13237600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13210500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12349600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9263100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9365300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8937500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7748200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7527600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5594600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5574000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5644700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5570900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10839600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10392900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11080700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11270200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10676100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10011200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9951900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10161900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10195400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9307300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>14815400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>12581600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11188800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>9796900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>8866400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>7244600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3486100</v>
+      </c>
+      <c r="E62" s="3">
         <v>3247100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3540600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3001300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2803300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3363200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3060500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2622500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2366100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2136900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2605800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2188200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2092800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1974200</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27459000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26910300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25827800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25192800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24294200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25390700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23974900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23110500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21910700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21228900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22212300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22853100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22492300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22372600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34868300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32673600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33000100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33684100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31773500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29984000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24891000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21865800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19617200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18861700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23183400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21561900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>25575700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>25671400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24663900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23406300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22545400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23472800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>23027900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>21419200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>27781400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>25176000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>23617300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>21678700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>19942300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>18116200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,95 +7938,98 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-323700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>191600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>184000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>362600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>320200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>808100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>760500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>607600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>796200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>660700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1114000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1160300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1156100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1748100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1869500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2803100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3805900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3647800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3031800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2133800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1408800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>335800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-36400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-574300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-871900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>609600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>456800</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>5</v>
       </c>
@@ -7871,8 +8045,8 @@
       <c r="AJ72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK72" s="3">
-        <v>0</v>
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL72" s="3">
         <v>0</v>
@@ -7889,8 +8063,11 @@
       <c r="AP72" s="3">
         <v>0</v>
       </c>
+      <c r="AQ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9014500</v>
+      </c>
+      <c r="E76" s="3">
         <v>8370800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8665500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8392500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8352300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7978100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8212300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7007700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6833600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6955100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6816800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7132800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7219400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7090800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7655900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7585700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8631200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9660000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9422900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9054000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8406200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7844200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6652000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6179900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5661000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5384600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7009800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6714400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6308400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6468600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6379200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6987500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7047300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6514200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6634500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6586000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6510700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6658400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6461000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6297300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1229200</v>
+      </c>
+      <c r="E81" s="3">
         <v>649700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1015200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>624900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>764200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>614900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>703900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>780800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>444400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>847400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>151800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>552000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>601300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>85800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>557900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-29400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1216900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1398500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1401900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1309200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1747900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>748900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>794700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>568300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1066500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>483100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>779400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>305800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>481300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>442700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>742000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>367900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>304100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>377900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>337400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>451900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>368000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>312900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,58 +8990,59 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E83" s="3">
         <v>13300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>47300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>69200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-15100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>14800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14900</v>
-      </c>
-      <c r="S83" s="3">
-        <v>18700</v>
       </c>
       <c r="T83" s="3">
         <v>18700</v>
@@ -8858,10 +9057,10 @@
         <v>18700</v>
       </c>
       <c r="X83" s="3">
+        <v>18700</v>
+      </c>
+      <c r="Y83" s="3">
         <v>18800</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>17800</v>
       </c>
       <c r="Z83" s="3">
         <v>17800</v>
@@ -8873,10 +9072,10 @@
         <v>17800</v>
       </c>
       <c r="AC83" s="3">
+        <v>17800</v>
+      </c>
+      <c r="AD83" s="3">
         <v>17700</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>17800</v>
       </c>
       <c r="AE83" s="3">
         <v>17800</v>
@@ -8885,10 +9084,10 @@
         <v>17800</v>
       </c>
       <c r="AG83" s="3">
+        <v>17800</v>
+      </c>
+      <c r="AH83" s="3">
         <v>15600</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>14500</v>
       </c>
       <c r="AI83" s="3">
         <v>14500</v>
@@ -8897,10 +9096,10 @@
         <v>14500</v>
       </c>
       <c r="AK83" s="3">
+        <v>14500</v>
+      </c>
+      <c r="AL83" s="3">
         <v>13900</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>11000</v>
       </c>
       <c r="AM83" s="3">
         <v>11000</v>
@@ -8909,13 +9108,16 @@
         <v>11000</v>
       </c>
       <c r="AO83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AP83" s="3">
         <v>15600</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1941400</v>
+      </c>
+      <c r="E89" s="3">
         <v>991000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1067800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1597600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>888500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1109200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>161400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1221900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1158600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>939800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>895700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1082900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1725600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>352700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>715100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>982900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1889700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2748500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-813900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1603700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>899600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2296700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>310000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>135100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>491300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>999500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>589900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1078400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>164300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>130500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1385600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1320900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-890800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1769800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-395500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-808700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-974600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>552500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-1203600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>415400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-29300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-31300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-62700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-60700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-69600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-48700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-85400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-45200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-56200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-45400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-60700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-75000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-48700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-85400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-45200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-56200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-14100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-20700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-95900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-45400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-107800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-179200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-13300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>6400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-16400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>924100</v>
+      </c>
+      <c r="E96" s="3">
         <v>1165100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1007600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>803500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>721800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1102800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>656300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>627900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>633100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>711900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>605100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>598300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>137600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1137300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1187900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1709200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1663700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1958000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1398900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-925300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1023300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1255100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-659400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-471500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-474000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-780800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-602900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-610200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-453400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-730300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-783600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-773500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-426600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1062700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-532300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-673000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1043700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-593600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-509600</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-433300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1844800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1093900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1019600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1287300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1711100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>139200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-489900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1279100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1216500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1516000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-712300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1400600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1189600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1751500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>238500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1624300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1500600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-908100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2090100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>957200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1281300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1362400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-872200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>295000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-549100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1117700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-893100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-31100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-129100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-868100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1079300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-971200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>453500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>266800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1497200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>498400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>463000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>312700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1275300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-126500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E101" s="3">
         <v>4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>14400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-10400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>9700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>21400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>18100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>33500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>56200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>16000</v>
       </c>
-      <c r="AO101" s="3">
-        <v>0</v>
-      </c>
       <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-144200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>22400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>282800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-850500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1223700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-357700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-67000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-71400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-599900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>162300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-385900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>474400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1472400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>919400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-738300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>333400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1779500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2925400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2548000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-394600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>907300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-649700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>394400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-66600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-137300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-320900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1035500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>20700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-756800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>198600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>347600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-451200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1486400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>947000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-283600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-459100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>871200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>55400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>286400</v>
       </c>
     </row>
